--- a/Data/network_data.xlsx
+++ b/Data/network_data.xlsx
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mazadi\LEC_Opt\LEC-Opt\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/araavind/Desktop/Python Files/LEC-Opt/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172B1945-839E-4040-86BD-8292C7701ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F1B074-C500-AF4B-99E8-354953AE52B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29040" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lines" sheetId="1" r:id="rId1"/>
     <sheet name="Loads" sheetId="2" r:id="rId2"/>
     <sheet name="BaseValues" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -423,15 +436,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -445,7 +458,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -459,7 +472,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -473,7 +486,7 @@
         <v>0.25109999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -487,7 +500,7 @@
         <v>0.18640000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -501,7 +514,7 @@
         <v>0.19409999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -515,7 +528,7 @@
         <v>0.70699999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -529,7 +542,7 @@
         <v>0.61880000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -543,7 +556,7 @@
         <v>1.2351000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -557,7 +570,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -571,7 +584,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -585,7 +598,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -599,7 +612,7 @@
         <v>0.12379999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
@@ -613,7 +626,7 @@
         <v>1.155</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -627,7 +640,7 @@
         <v>0.71289999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1</v>
       </c>
@@ -641,7 +654,7 @@
         <v>0.52600000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
@@ -655,7 +668,7 @@
         <v>0.54500000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
@@ -669,7 +682,7 @@
         <v>1.7210000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>16</v>
       </c>
@@ -683,7 +696,7 @@
         <v>0.57399999999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1</v>
       </c>
@@ -697,7 +710,7 @@
         <v>0.1565</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
@@ -711,7 +724,7 @@
         <v>1.3553999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
@@ -725,7 +738,7 @@
         <v>0.47839999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
@@ -739,7 +752,7 @@
         <v>0.93730000000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2</v>
       </c>
@@ -753,7 +766,7 @@
         <v>0.30830000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
@@ -767,7 +780,7 @@
         <v>0.70909999999999995</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
@@ -781,7 +794,7 @@
         <v>0.70109999999999995</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>23</v>
       </c>
@@ -795,7 +808,7 @@
         <v>0.70909999999999995</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>5</v>
       </c>
@@ -809,7 +822,7 @@
         <v>0.10340000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>25</v>
       </c>
@@ -823,7 +836,7 @@
         <v>0.1447</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>26</v>
       </c>
@@ -837,7 +850,7 @@
         <v>0.93369999999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>27</v>
       </c>
@@ -851,7 +864,7 @@
         <v>0.7006</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>28</v>
       </c>
@@ -865,7 +878,7 @@
         <v>0.25850000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>29</v>
       </c>
@@ -879,7 +892,7 @@
         <v>0.96299999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>30</v>
       </c>
@@ -893,7 +906,7 @@
         <v>0.3619</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>31</v>
       </c>
@@ -915,9 +928,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -928,7 +945,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -939,7 +956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -950,7 +967,7 @@
         <v>4.561503322165486E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -961,7 +978,7 @@
         <v>5.6843394886864851E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -972,7 +989,7 @@
         <v>1.878980043635514E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -983,7 +1000,7 @@
         <v>6.1763549707587712E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -994,7 +1011,7 @@
         <v>6.1209572272242142E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1005,7 +1022,7 @@
         <v>6.1693399687475697E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1016,7 +1033,7 @@
         <v>9.4374807851462419E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1027,7 +1044,7 @@
         <v>6.8182029910348343E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1038,7 +1055,7 @@
         <v>3.5950790057378612E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1049,7 +1066,7 @@
         <v>4.3703195379934147E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1060,7 +1077,7 @@
         <v>6.9763119592726491E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1071,7 +1088,7 @@
         <v>6.022547162926984E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1082,7 +1099,7 @@
         <v>6.6676671544566773E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1093,7 +1110,7 @@
         <v>6.7063786961815947E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1104,7 +1121,7 @@
         <v>2.1038256107384089E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1115,7 +1132,7 @@
         <v>1.2892629765485331E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1126,7 +1143,7 @@
         <v>3.1542835092418391E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1137,7 +1154,7 @@
         <v>3.6371077094262259E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1148,7 +1165,7 @@
         <v>5.7019677041787967E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1159,7 +1176,7 @@
         <v>4.3860151346232043E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1170,7 +1187,7 @@
         <v>9.8837383805922621E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1181,7 +1198,7 @@
         <v>1.0204481074802809E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1192,7 +1209,7 @@
         <v>2.0887675609483469E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1203,7 +1220,7 @@
         <v>1.6130951788499631E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1214,7 +1231,7 @@
         <v>6.531083254653984E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1225,7 +1242,7 @@
         <v>2.532916025397821E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1236,7 +1253,7 @@
         <v>4.663107728563063E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1247,7 +1264,7 @@
         <v>2.444255920016028E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1258,7 +1275,7 @@
         <v>1.5896958364551971E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1269,7 +1286,7 @@
         <v>1.1037514116430509E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1280,7 +1297,7 @@
         <v>6.5632958946527348E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1299,9 +1316,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1309,7 +1326,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1317,7 +1334,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
